--- a/data/trans_camb/P57_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Estudios-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 15,03</t>
+          <t>4,65; 14,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 12,29</t>
+          <t>5,2; 12,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,94</t>
+          <t>6,2; 12,23</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,17; 68,63</t>
+          <t>18,18; 66,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,18; 75,91</t>
+          <t>26,42; 81,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,51; 62,2</t>
+          <t>27,8; 62,96</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,25; 38,85</t>
+          <t>18,23; 39,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 16,86</t>
+          <t>-0,57; 17,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 26,3</t>
+          <t>11,92; 26,68</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,32; 123,32</t>
+          <t>58,21; 130,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 60,27</t>
+          <t>-1,7; 61,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,83; 89,08</t>
+          <t>40,72; 92,01</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,56</t>
+          <t>3,07; 15,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 16,1</t>
+          <t>5,52; 16,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 14,18</t>
+          <t>6,11; 14,18</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 43,91</t>
+          <t>7,35; 43,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,71; 52,18</t>
+          <t>14,88; 51,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,09; 41,27</t>
+          <t>15,97; 41,72</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,7; 30,78</t>
+          <t>15,67; 31,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 14,86</t>
+          <t>5,46; 15,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,14; 21,73</t>
+          <t>11,64; 21,89</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50,65; 100,36</t>
+          <t>50,61; 106,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,17; 57,01</t>
+          <t>20,31; 58,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41,41; 76,56</t>
+          <t>40,71; 78,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>10,3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,82</t>
+          <t>8,23</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>8,98</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 14,61</t>
+          <t>5,54; 15,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 12,95</t>
+          <t>4,78; 11,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 12,23</t>
+          <t>6,16; 11,92</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 66,49</t>
+          <t>21,67; 72,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,42; 81,77</t>
+          <t>24,26; 72,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,8; 62,96</t>
+          <t>28,57; 63,23</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24,49</t>
+          <t>18,39</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>17,4</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>17,89</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 39,56</t>
+          <t>15,17; 21,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 17,15</t>
+          <t>14,57; 20,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 26,68</t>
+          <t>15,79; 19,86</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,21; 130,35</t>
+          <t>46,95; 74,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 61,25</t>
+          <t>48,3; 75,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,72; 92,01</t>
+          <t>51,12; 69,14</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,02</t>
+          <t>10,27</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,16</t>
+          <t>9,66</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 15,24</t>
+          <t>3,25; 15,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 16,11</t>
+          <t>5,03; 15,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 14,18</t>
+          <t>5,71; 14,04</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 43,45</t>
+          <t>7,36; 42,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,88; 51,58</t>
+          <t>13,07; 49,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,97; 41,72</t>
+          <t>15,07; 41,9</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>20,23</t>
+          <t>15,94</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11,62</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>15,4</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,67; 31,43</t>
+          <t>13,34; 18,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 15,07</t>
+          <t>12,77; 16,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,64; 21,89</t>
+          <t>13,84; 17,04</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50,61; 106,04</t>
+          <t>42,29; 63,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,31; 58,74</t>
+          <t>45,67; 66,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,71; 78,44</t>
+          <t>47,72; 62,11</t>
         </is>
       </c>
     </row>
